--- a/data/trans_bre/P5_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 7,43</t>
+          <t>-15,84; 7,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 8,36</t>
+          <t>-12,36; 9,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 8,79</t>
+          <t>-12,19; 8,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 19,13</t>
+          <t>-2,22; 18,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 27,51</t>
+          <t>-40,26; 24,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 24,95</t>
+          <t>-27,79; 26,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 32,01</t>
+          <t>-31,34; 31,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 226,49</t>
+          <t>-12,92; 206,53</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 12,8</t>
+          <t>-2,03; 12,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 3,55</t>
+          <t>-14,39; 3,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 7,14</t>
+          <t>-9,3; 7,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 8,57</t>
+          <t>-6,95; 8,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 69,27</t>
+          <t>-8,18; 67,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 10,22</t>
+          <t>-32,89; 9,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 22,77</t>
+          <t>-23,98; 21,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 47,09</t>
+          <t>-27,87; 44,86</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 8,95</t>
+          <t>-12,84; 8,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 14,32</t>
+          <t>-7,86; 14,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 6,13</t>
+          <t>-12,47; 7,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 6,11</t>
+          <t>-7,31; 7,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 33,37</t>
+          <t>-35,34; 32,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 49,02</t>
+          <t>-19,58; 51,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 17,26</t>
+          <t>-27,72; 20,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 40,73</t>
+          <t>-34,23; 49,5</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 6,69</t>
+          <t>-10,01; 6,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 15,33</t>
+          <t>-4,78; 15,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 4,94</t>
+          <t>-15,52; 5,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 32,83</t>
+          <t>-1,99; 31,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 28,03</t>
+          <t>-29,87; 27,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 47,15</t>
+          <t>-10,91; 48,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 14,54</t>
+          <t>-33,57; 16,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 253,22</t>
+          <t>-14,96; 241,8</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,42</t>
+          <t>-4,46; 4,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,99</t>
+          <t>-5,31; 4,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,74</t>
+          <t>-6,96; 2,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 15,42</t>
+          <t>-0,52; 14,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 17,42</t>
+          <t>-14,53; 17,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 14,08</t>
+          <t>-12,94; 13,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 7,8</t>
+          <t>-17,8; 6,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 94,72</t>
+          <t>-3,43; 93,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 7,09</t>
+          <t>-16,34; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 9,7</t>
+          <t>-12,8; 9,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 8,73</t>
+          <t>-12,13; 8,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 18,78</t>
+          <t>-1,94; 19,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 24,93</t>
+          <t>-41,71; 24,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 26,94</t>
+          <t>-28,52; 26,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 31,44</t>
+          <t>-29,33; 32,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 206,53</t>
+          <t>-13,27; 211,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 12,51</t>
+          <t>-2,23; 12,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 3,42</t>
+          <t>-13,39; 3,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 7,01</t>
+          <t>-8,53; 7,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 8,55</t>
+          <t>-6,7; 8,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 67,67</t>
+          <t>-9,11; 64,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 9,59</t>
+          <t>-31,56; 10,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 21,44</t>
+          <t>-21,63; 22,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 44,86</t>
+          <t>-26,54; 47,1</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 8,73</t>
+          <t>-12,2; 8,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 14,82</t>
+          <t>-7,88; 15,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 7,49</t>
+          <t>-11,75; 7,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 7,23</t>
+          <t>-7,56; 7,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 32,88</t>
+          <t>-35,35; 31,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 51,73</t>
+          <t>-20,6; 56,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 20,68</t>
+          <t>-26,97; 21,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 49,5</t>
+          <t>-35,01; 47,74</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 6,66</t>
+          <t>-9,58; 7,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 15,93</t>
+          <t>-5,65; 15,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 5,8</t>
+          <t>-15,51; 5,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 31,43</t>
+          <t>-1,95; 30,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 27,18</t>
+          <t>-29,26; 29,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 48,33</t>
+          <t>-12,6; 45,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 16,54</t>
+          <t>-34,07; 15,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 241,8</t>
+          <t>-14,06; 257,4</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,56</t>
+          <t>-4,13; 4,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,87</t>
+          <t>-5,29; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 2,36</t>
+          <t>-7,73; 2,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,4</t>
+          <t>-0,59; 14,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 17,81</t>
+          <t>-13,9; 17,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 13,67</t>
+          <t>-12,98; 12,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 6,8</t>
+          <t>-18,99; 6,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 93,96</t>
+          <t>-3,99; 92,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,49</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 6,66</t>
+          <t>-15,92; 7,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 9,02</t>
+          <t>-13,1; 8,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 8,94</t>
+          <t>-11,81; 8,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 19,1</t>
+          <t>-5,0; 19,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 24,48</t>
+          <t>-39,45; 27,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 26,54</t>
+          <t>-28,72; 24,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 32,6</t>
+          <t>-31,56; 32,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 211,22</t>
+          <t>-27,03; 183,18</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>-0,91%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 12,18</t>
+          <t>-2,04; 12,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 3,32</t>
+          <t>-13,92; 3,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 7,05</t>
+          <t>-8,88; 7,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 8,71</t>
+          <t>-7,2; 7,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 64,7</t>
+          <t>-7,76; 69,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 10,24</t>
+          <t>-32,5; 10,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 22,65</t>
+          <t>-22,53; 22,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 47,1</t>
+          <t>-27,45; 40,79</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,19%</t>
+          <t>-1,29%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 8,32</t>
+          <t>-12,89; 8,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 15,32</t>
+          <t>-7,69; 14,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 7,28</t>
+          <t>-13,13; 6,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 7,08</t>
+          <t>-7,71; 6,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 31,46</t>
+          <t>-36,47; 33,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 56,14</t>
+          <t>-21,56; 49,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 21,95</t>
+          <t>-29,21; 17,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 47,74</t>
+          <t>-34,53; 39,31</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 7,2</t>
+          <t>-9,45; 6,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 15,28</t>
+          <t>-6,45; 15,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 5,45</t>
+          <t>-16,02; 4,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 30,66</t>
+          <t>-3,83; 7,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 29,92</t>
+          <t>-28,78; 28,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 45,83</t>
+          <t>-14,25; 47,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 15,98</t>
+          <t>-34,62; 14,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 257,4</t>
+          <t>-24,44; 63,68</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,53</t>
+          <t>-4,22; 4,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,48</t>
+          <t>-5,4; 4,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,14</t>
+          <t>-7,02; 2,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 14,73</t>
+          <t>-2,68; 4,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 17,33</t>
+          <t>-14,08; 17,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 12,29</t>
+          <t>-12,86; 14,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 6,08</t>
+          <t>-17,94; 7,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 92,1</t>
+          <t>-14,1; 30,7</t>
         </is>
       </c>
     </row>
